--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>113188927</v>
       </c>
       <c r="B5" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>113188927</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>113188927</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>113188927</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>113188927</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 67294-2018 artfynd.xlsx
+++ b/artfynd/A 67294-2018 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
